--- a/inasistencias-7A-CompAero/Alumnos-⁄A-CompAero.xlsx
+++ b/inasistencias-7A-CompAero/Alumnos-⁄A-CompAero.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="784" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="919" uniqueCount="121">
   <si>
     <t xml:space="preserve">nRO</t>
   </si>
@@ -339,7 +339,31 @@
     <t xml:space="preserve">Valoracion</t>
   </si>
   <si>
+    <t xml:space="preserve">val ped</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grupo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">proyecto Arinc 429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4-DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3-Desarrollo</t>
+  </si>
+  <si>
     <t xml:space="preserve">BARRERA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2-Hacker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1-instalador</t>
   </si>
   <si>
     <t xml:space="preserve">DEL MASTRO</t>
@@ -505,7 +529,50 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="6">
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <charset val="1"/>
+        <family val="0"/>
+        <color rgb="FF006600"/>
+        <sz val="12"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFCCFFCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <charset val="1"/>
+        <family val="0"/>
+        <color rgb="FFCC0000"/>
+        <sz val="12"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFCCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <charset val="1"/>
+        <family val="0"/>
+        <b val="1"/>
+        <color rgb="FFFFFFFF"/>
+        <sz val="12"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFCC0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <name val="Calibri"/>
@@ -724,7 +791,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:BQ32"/>
+  <dimension ref="A1:XDE32"/>
   <sheetFormatPr defaultColWidth="8.87109375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4.87"/>
@@ -734,7 +801,8 @@
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="5" min="5" style="1" width="8.72"/>
     <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="14" min="6" style="1" width="8.87"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="15" min="15" style="1" width="12.55"/>
-    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="20" min="16" style="1" width="8.87"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="31" min="16" style="1" width="8.87"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16333" min="16332" style="0" width="10.58"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16334" style="1" width="10.58"/>
   </cols>
   <sheetData>
@@ -851,74 +919,70 @@
         <v>46220</v>
       </c>
       <c r="AK2" s="3" t="n">
-        <v>46227</v>
+        <v>46241</v>
       </c>
       <c r="AL2" s="3" t="n">
-        <v>46234</v>
+        <v>46248</v>
       </c>
       <c r="AM2" s="3" t="n">
-        <v>46241</v>
+        <v>46255</v>
       </c>
       <c r="AN2" s="3" t="n">
-        <v>46248</v>
+        <v>46262</v>
       </c>
       <c r="AO2" s="3" t="n">
-        <v>46255</v>
+        <v>46269</v>
       </c>
       <c r="AP2" s="3" t="n">
-        <v>46262</v>
+        <v>46276</v>
       </c>
       <c r="AQ2" s="3" t="n">
-        <v>46269</v>
+        <v>46283</v>
       </c>
       <c r="AR2" s="3" t="n">
-        <v>46276</v>
+        <v>46290</v>
       </c>
       <c r="AS2" s="3" t="n">
-        <v>46283</v>
+        <v>46297</v>
       </c>
       <c r="AT2" s="3" t="n">
-        <v>46290</v>
+        <v>46304</v>
       </c>
       <c r="AU2" s="3" t="n">
-        <v>46297</v>
+        <v>46311</v>
       </c>
       <c r="AV2" s="3" t="n">
-        <v>46304</v>
+        <v>46318</v>
       </c>
       <c r="AW2" s="3" t="n">
-        <v>46311</v>
+        <v>46325</v>
       </c>
       <c r="AX2" s="3" t="n">
-        <v>46318</v>
+        <v>46332</v>
       </c>
       <c r="AY2" s="3" t="n">
-        <v>46325</v>
+        <v>46339</v>
       </c>
       <c r="AZ2" s="3" t="n">
-        <v>46332</v>
+        <v>46346</v>
       </c>
       <c r="BA2" s="3" t="n">
-        <v>46339</v>
+        <v>46353</v>
       </c>
       <c r="BB2" s="3" t="n">
-        <v>46346</v>
+        <v>46360</v>
       </c>
       <c r="BC2" s="3" t="n">
-        <v>46353</v>
+        <v>46367</v>
       </c>
       <c r="BD2" s="3" t="n">
-        <v>46360</v>
+        <v>46374</v>
       </c>
       <c r="BE2" s="3" t="n">
-        <v>46367</v>
-      </c>
-      <c r="BF2" s="3" t="n">
-        <v>46374</v>
-      </c>
-      <c r="BG2" s="3" t="n">
         <v>46381</v>
       </c>
+      <c r="BF2" s="3"/>
+      <c r="BG2" s="3"/>
       <c r="BH2" s="3"/>
       <c r="BI2" s="3"/>
       <c r="BJ2" s="3"/>
@@ -927,8 +991,6 @@
       <c r="BM2" s="3"/>
       <c r="BN2" s="3"/>
       <c r="BO2" s="3"/>
-      <c r="BP2" s="3"/>
-      <c r="BQ2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
@@ -1021,8 +1083,20 @@
       <c r="AE3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="AF3" s="6" t="s">
-        <v>17</v>
+      <c r="AF3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AG3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AH3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AJ3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AK3" s="6" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1098,7 +1172,19 @@
       <c r="AE4" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AF4" s="6" t="s">
+      <c r="AF4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AG4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AH4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AJ4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AK4" s="6" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1187,7 +1273,19 @@
       <c r="AE5" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AF5" s="6" t="s">
+      <c r="AF5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AG5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AH5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AJ5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AK5" s="6" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1276,7 +1374,19 @@
       <c r="AE6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AF6" s="6" t="s">
+      <c r="AF6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AG6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AH6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AJ6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AK6" s="6" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1362,7 +1472,19 @@
       <c r="AE7" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AF7" s="6" t="s">
+      <c r="AF7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AG7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AH7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AJ7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AK7" s="6" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1442,8 +1564,20 @@
       <c r="AE8" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="AF8" s="6" t="s">
-        <v>17</v>
+      <c r="AF8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AG8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AH8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AJ8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AK8" s="6" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1522,7 +1656,19 @@
       <c r="AE9" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AF9" s="6" t="s">
+      <c r="AF9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AG9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AH9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AJ9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AK9" s="6" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1605,7 +1751,19 @@
       <c r="AE10" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AF10" s="6" t="s">
+      <c r="AF10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AG10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AH10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AJ10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AK10" s="6" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1682,7 +1840,19 @@
       <c r="AE11" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AF11" s="6" t="s">
+      <c r="AF11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AG11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AH11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AJ11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AK11" s="6" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1765,7 +1935,19 @@
       <c r="AE12" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AF12" s="6" t="s">
+      <c r="AF12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AG12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AH12" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AJ12" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AK12" s="6" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1842,7 +2024,19 @@
       <c r="AE13" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AF13" s="6" t="s">
+      <c r="AF13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AG13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AH13" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AJ13" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AK13" s="6" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1928,7 +2122,19 @@
       <c r="AE14" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="AF14" s="6" t="s">
+      <c r="AF14" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AG14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AH14" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AJ14" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AK14" s="6" t="s">
         <v>17</v>
       </c>
     </row>
@@ -2005,8 +2211,20 @@
       <c r="AE15" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AF15" s="6" t="s">
-        <v>17</v>
+      <c r="AF15" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AG15" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AH15" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AJ15" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AK15" s="6" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2082,7 +2300,19 @@
       <c r="AE16" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AF16" s="6" t="s">
+      <c r="AF16" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AG16" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AH16" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AJ16" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AK16" s="6" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2162,7 +2392,19 @@
       <c r="AE17" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="AF17" s="6" t="s">
+      <c r="AF17" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AG17" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AH17" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AJ17" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AK17" s="6" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2248,7 +2490,19 @@
       <c r="AE18" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AF18" s="6" t="s">
+      <c r="AF18" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AG18" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AH18" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AJ18" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AK18" s="6" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2328,7 +2582,19 @@
       <c r="AE19" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AF19" s="6" t="s">
+      <c r="AF19" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AG19" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AH19" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AJ19" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AK19" s="6" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2411,7 +2677,19 @@
       <c r="AE20" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="AF20" s="6" t="s">
+      <c r="AF20" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AG20" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AH20" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AJ20" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AK20" s="6" t="s">
         <v>17</v>
       </c>
     </row>
@@ -2491,6 +2769,20 @@
       <c r="AF21" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="AG21" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AH21" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AJ21" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AK21" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="XDD21" s="0"/>
+      <c r="XDE21" s="0"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="n">
@@ -2571,8 +2863,20 @@
       <c r="AE22" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AF22" s="6" t="s">
-        <v>17</v>
+      <c r="AF22" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AG22" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AH22" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AJ22" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AK22" s="6" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2651,7 +2955,19 @@
       <c r="AE23" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AF23" s="6" t="s">
+      <c r="AF23" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AG23" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AH23" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AJ23" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AK23" s="6" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2731,7 +3047,19 @@
       <c r="AE24" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AF24" s="6" t="s">
+      <c r="AF24" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AG24" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AH24" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AJ24" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AK24" s="6" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2811,7 +3139,19 @@
       <c r="AE25" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AF25" s="6" t="s">
+      <c r="AF25" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AG25" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AH25" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AJ25" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AK25" s="6" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2888,7 +3228,19 @@
       <c r="AE26" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AF26" s="6" t="s">
+      <c r="AF26" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AG26" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AH26" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AJ26" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AK26" s="6" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2971,7 +3323,19 @@
       <c r="AE27" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AF27" s="6" t="s">
+      <c r="AF27" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AG27" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AH27" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AJ27" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AK27" s="6" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3060,7 +3424,19 @@
       <c r="AE28" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AF28" s="6" t="s">
+      <c r="AF28" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AG28" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AH28" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AJ28" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AK28" s="6" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3100,12 +3476,10 @@
         <f aca="false">COUNTIF(T3:T28,"p")</f>
         <v>17</v>
       </c>
-      <c r="U29" s="1"/>
       <c r="V29" s="1" t="n">
         <f aca="false">COUNTIF(V3:V28,"p")</f>
         <v>13</v>
       </c>
-      <c r="W29" s="1"/>
       <c r="AD29" s="1" t="n">
         <f aca="false">COUNTIF(AD3:AD28,"p")</f>
         <v>24</v>
@@ -3118,6 +3492,21 @@
         <f aca="false">COUNTIF(AF3:AF28,"p")</f>
         <v>20</v>
       </c>
+      <c r="AG29" s="1" t="n">
+        <f aca="false">COUNTIF(AG3:AG28,"p")</f>
+        <v>20</v>
+      </c>
+      <c r="AH29" s="1" t="n">
+        <f aca="false">COUNTIF(AH3:AH28,"p")</f>
+        <v>11</v>
+      </c>
+      <c r="AI29" s="1"/>
+      <c r="AJ29" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="AK29" s="1" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C30" s="1" t="s">
@@ -3155,12 +3544,10 @@
         <f aca="false">COUNTIF(T3:T28,"M")</f>
         <v>0</v>
       </c>
-      <c r="U30" s="1"/>
       <c r="V30" s="1" t="n">
         <f aca="false">COUNTIF(V3:V28,"M")</f>
         <v>1</v>
       </c>
-      <c r="W30" s="1"/>
       <c r="AD30" s="1" t="n">
         <f aca="false">COUNTIF(AD3:AD28,"M")</f>
         <v>0</v>
@@ -3173,6 +3560,21 @@
         <f aca="false">COUNTIF(AF3:AF28,"M")</f>
         <v>0</v>
       </c>
+      <c r="AG30" s="1" t="n">
+        <f aca="false">COUNTIF(AG3:AG28,"M")</f>
+        <v>0</v>
+      </c>
+      <c r="AH30" s="1" t="n">
+        <f aca="false">COUNTIF(AH3:AH28,"M")</f>
+        <v>0</v>
+      </c>
+      <c r="AI30" s="1"/>
+      <c r="AJ30" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK30" s="1" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C31" s="1" t="s">
@@ -3210,12 +3612,10 @@
         <f aca="false">COUNTIF(T3:T28,"T")</f>
         <v>4</v>
       </c>
-      <c r="U31" s="1"/>
       <c r="V31" s="1" t="n">
         <f aca="false">COUNTIF(V3:V28,"T")</f>
         <v>2</v>
       </c>
-      <c r="W31" s="1"/>
       <c r="AD31" s="1" t="n">
         <f aca="false">COUNTIF(AD3:AD28,"T")</f>
         <v>0</v>
@@ -3228,6 +3628,21 @@
         <f aca="false">COUNTIF(AF3:AF28,"T")</f>
         <v>0</v>
       </c>
+      <c r="AG31" s="1" t="n">
+        <f aca="false">COUNTIF(AG3:AG28,"T")</f>
+        <v>0</v>
+      </c>
+      <c r="AH31" s="1" t="n">
+        <f aca="false">COUNTIF(AH3:AH28,"T")</f>
+        <v>0</v>
+      </c>
+      <c r="AI31" s="1"/>
+      <c r="AJ31" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK31" s="1" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C32" s="1" t="s">
@@ -3265,12 +3680,10 @@
         <f aca="false">SUM(T29:T31)</f>
         <v>21</v>
       </c>
-      <c r="U32" s="1"/>
       <c r="V32" s="1" t="n">
         <f aca="false">SUM(V29:V31)</f>
         <v>16</v>
       </c>
-      <c r="W32" s="1"/>
       <c r="AD32" s="1" t="n">
         <f aca="false">SUM(AD29:AD31)</f>
         <v>24</v>
@@ -3282,6 +3695,21 @@
       <c r="AF32" s="1" t="n">
         <f aca="false">SUM(AF29:AF31)</f>
         <v>20</v>
+      </c>
+      <c r="AG32" s="1" t="n">
+        <f aca="false">SUM(AG29:AG31)</f>
+        <v>20</v>
+      </c>
+      <c r="AH32" s="1" t="n">
+        <f aca="false">SUM(AH29:AH31)</f>
+        <v>11</v>
+      </c>
+      <c r="AI32" s="1"/>
+      <c r="AJ32" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="AK32" s="1" t="n">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -3312,12 +3740,19 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M35"/>
+  <dimension ref="A1:R35"/>
   <sheetFormatPr defaultColWidth="9.71484375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4.43"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18.54"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16304" style="1" width="10.58"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="4" min="4" style="1" width="9.71"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="6" min="6" style="1" width="9.71"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="8" min="8" style="1" width="9.71"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="10" min="10" style="1" width="9.71"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="13" min="13" style="1" width="9.71"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="14" min="14" style="1" width="17.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="15" style="1" width="17.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16306" style="1" width="10.58"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3357,6 +3792,21 @@
       <c r="M1" s="1" t="s">
         <v>103</v>
       </c>
+      <c r="N1" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="n">
@@ -3365,7 +3815,7 @@
       <c r="B2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="5" t="n">
+      <c r="C2" s="1" t="n">
         <v>9</v>
       </c>
       <c r="E2" s="1" t="n">
@@ -3388,6 +3838,24 @@
         <f aca="false">IF(L2&gt;6,"TEA",IF(L2&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
+      <c r="N2" s="1" t="str">
+        <f aca="false">IF(L2&gt;6,"TEA",IF(L2&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="P2" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q2" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(L2,P2),0)</f>
+        <v>8</v>
+      </c>
+      <c r="R2" s="5" t="str">
+        <f aca="false">IF(Q2&gt;6,"TEA",IF(Q2&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
@@ -3396,7 +3864,7 @@
       <c r="B3" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="5" t="n">
+      <c r="C3" s="1" t="n">
         <v>6</v>
       </c>
       <c r="E3" s="1" t="n">
@@ -3419,15 +3887,33 @@
         <f aca="false">IF(L3&gt;6,"TEA",IF(L3&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
+      <c r="N3" s="1" t="str">
+        <f aca="false">IF(L3&gt;6,"TEA",IF(L3&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="P3" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q3" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(L3,P3),0)</f>
+        <v>9</v>
+      </c>
+      <c r="R3" s="5" t="str">
+        <f aca="false">IF(Q3&gt;6,"TEA",IF(Q3&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="n">
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C4" s="5" t="n">
+        <v>110</v>
+      </c>
+      <c r="C4" s="1" t="n">
         <v>9</v>
       </c>
       <c r="E4" s="1" t="n">
@@ -3450,6 +3936,24 @@
         <f aca="false">IF(L4&gt;6,"TEA",IF(L4&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
+      <c r="N4" s="1" t="str">
+        <f aca="false">IF(L4&gt;6,"TEA",IF(L4&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="P4" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q4" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(L4,P4),0)</f>
+        <v>8</v>
+      </c>
+      <c r="R4" s="5" t="str">
+        <f aca="false">IF(Q4&gt;6,"TEA",IF(Q4&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="n">
@@ -3458,7 +3962,7 @@
       <c r="B5" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C5" s="5" t="n">
+      <c r="C5" s="1" t="n">
         <v>7</v>
       </c>
       <c r="E5" s="1" t="n">
@@ -3481,6 +3985,24 @@
         <f aca="false">IF(L5&gt;6,"TEA",IF(L5&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
+      <c r="N5" s="1" t="str">
+        <f aca="false">IF(L5&gt;6,"TEA",IF(L5&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="P5" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q5" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(L5,P5),0)</f>
+        <v>8</v>
+      </c>
+      <c r="R5" s="5" t="str">
+        <f aca="false">IF(Q5&gt;6,"TEA",IF(Q5&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="n">
@@ -3489,7 +4011,7 @@
       <c r="B6" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="5" t="n">
+      <c r="C6" s="1" t="n">
         <v>10</v>
       </c>
       <c r="E6" s="1" t="n">
@@ -3512,6 +4034,24 @@
         <f aca="false">IF(L6&gt;6,"TEA",IF(L6&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
+      <c r="N6" s="1" t="str">
+        <f aca="false">IF(L6&gt;6,"TEA",IF(L6&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
+      <c r="O6" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="P6" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q6" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(L6,P6),0)</f>
+        <v>10</v>
+      </c>
+      <c r="R6" s="5" t="str">
+        <f aca="false">IF(Q6&gt;6,"TEA",IF(Q6&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="n">
@@ -3520,28 +4060,55 @@
       <c r="B7" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="5" t="n">
-        <v>1</v>
+      <c r="C7" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>46171</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>46171</v>
       </c>
       <c r="G7" s="1" t="n">
         <v>6</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>46171</v>
       </c>
       <c r="K7" s="1" t="n">
         <v>4</v>
       </c>
       <c r="L7" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(C7,E7,G7,I7,K7),0)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M7" s="1" t="str">
         <f aca="false">IF(L7&gt;6,"TEA",IF(L7&gt;3,"TEP","TED"))</f>
-        <v>TED</v>
+        <v>TEP</v>
+      </c>
+      <c r="N7" s="1" t="str">
+        <f aca="false">IF(L7&gt;6,"TEA",IF(L7&gt;3,"TEP","TED"))</f>
+        <v>TEP</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="P7" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q7" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(L7,P7),0)</f>
+        <v>6</v>
+      </c>
+      <c r="R7" s="5" t="str">
+        <f aca="false">IF(Q7&gt;6,"TEA",IF(Q7&gt;3,"TEP","TED"))</f>
+        <v>TEP</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3551,7 +4118,7 @@
       <c r="B8" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C8" s="5" t="n">
+      <c r="C8" s="1" t="n">
         <v>8</v>
       </c>
       <c r="E8" s="1" t="n">
@@ -3574,6 +4141,24 @@
         <f aca="false">IF(L8&gt;6,"TEA",IF(L8&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
+      <c r="N8" s="1" t="str">
+        <f aca="false">IF(L8&gt;6,"TEA",IF(L8&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="P8" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q8" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(L8,P8),0)</f>
+        <v>10</v>
+      </c>
+      <c r="R8" s="5" t="str">
+        <f aca="false">IF(Q8&gt;6,"TEA",IF(Q8&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="n">
@@ -3582,7 +4167,7 @@
       <c r="B9" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="5" t="n">
+      <c r="C9" s="1" t="n">
         <v>9</v>
       </c>
       <c r="E9" s="1" t="n">
@@ -3605,6 +4190,24 @@
         <f aca="false">IF(L9&gt;6,"TEA",IF(L9&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
+      <c r="N9" s="1" t="str">
+        <f aca="false">IF(L9&gt;6,"TEA",IF(L9&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
+      <c r="O9" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="P9" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q9" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(L9,P9),0)</f>
+        <v>10</v>
+      </c>
+      <c r="R9" s="5" t="str">
+        <f aca="false">IF(Q9&gt;6,"TEA",IF(Q9&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="n">
@@ -3613,7 +4216,7 @@
       <c r="B10" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="5" t="n">
+      <c r="C10" s="1" t="n">
         <v>10</v>
       </c>
       <c r="E10" s="1" t="n">
@@ -3636,15 +4239,33 @@
         <f aca="false">IF(L10&gt;6,"TEA",IF(L10&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
+      <c r="N10" s="1" t="str">
+        <f aca="false">IF(L10&gt;6,"TEA",IF(L10&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
+      <c r="O10" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="P10" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q10" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(L10,P10),0)</f>
+        <v>10</v>
+      </c>
+      <c r="R10" s="5" t="str">
+        <f aca="false">IF(Q10&gt;6,"TEA",IF(Q10&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
     </row>
     <row r="11" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="n">
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C11" s="5" t="n">
+        <v>113</v>
+      </c>
+      <c r="C11" s="1" t="n">
         <v>8</v>
       </c>
       <c r="E11" s="1" t="n">
@@ -3654,18 +4275,39 @@
         <v>8</v>
       </c>
       <c r="I11" s="1" t="n">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="J11" s="3" t="n">
+        <v>46171</v>
       </c>
       <c r="K11" s="1" t="n">
         <v>7</v>
       </c>
       <c r="L11" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(C11,E11,G11,I11,K11),0)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M11" s="1" t="str">
         <f aca="false">IF(L11&gt;6,"TEA",IF(L11&gt;3,"TEP","TED"))</f>
-        <v>TEP</v>
+        <v>TEA</v>
+      </c>
+      <c r="N11" s="1" t="str">
+        <f aca="false">IF(L11&gt;6,"TEA",IF(L11&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
+      <c r="O11" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="P11" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q11" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(L11,P11),0)</f>
+        <v>7</v>
+      </c>
+      <c r="R11" s="5" t="str">
+        <f aca="false">IF(Q11&gt;6,"TEA",IF(Q11&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3675,7 +4317,7 @@
       <c r="B12" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C12" s="5" t="n">
+      <c r="C12" s="1" t="n">
         <v>10</v>
       </c>
       <c r="E12" s="1" t="n">
@@ -3698,6 +4340,24 @@
         <f aca="false">IF(L12&gt;6,"TEA",IF(L12&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
+      <c r="N12" s="1" t="str">
+        <f aca="false">IF(L12&gt;6,"TEA",IF(L12&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="P12" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q12" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(L12,P12),0)</f>
+        <v>10</v>
+      </c>
+      <c r="R12" s="5" t="str">
+        <f aca="false">IF(Q12&gt;6,"TEA",IF(Q12&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
     </row>
     <row r="13" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="n">
@@ -3706,7 +4366,7 @@
       <c r="B13" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C13" s="5" t="n">
+      <c r="C13" s="1" t="n">
         <v>9</v>
       </c>
       <c r="E13" s="1" t="n">
@@ -3716,18 +4376,39 @@
         <v>8</v>
       </c>
       <c r="I13" s="1" t="n">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="J13" s="3" t="n">
+        <v>46206</v>
       </c>
       <c r="K13" s="1" t="n">
         <v>4</v>
       </c>
       <c r="L13" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(C13,E13,G13,I13,K13),0)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M13" s="1" t="str">
         <f aca="false">IF(L13&gt;6,"TEA",IF(L13&gt;3,"TEP","TED"))</f>
-        <v>TEP</v>
+        <v>TEA</v>
+      </c>
+      <c r="N13" s="1" t="str">
+        <f aca="false">IF(L13&gt;6,"TEA",IF(L13&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="P13" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q13" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(L13,P13),0)</f>
+        <v>8</v>
+      </c>
+      <c r="R13" s="5" t="str">
+        <f aca="false">IF(Q13&gt;6,"TEA",IF(Q13&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="true" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3735,9 +4416,9 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="C14" s="5" t="n">
+        <v>114</v>
+      </c>
+      <c r="C14" s="1" t="n">
         <v>9</v>
       </c>
       <c r="E14" s="1" t="n">
@@ -3760,6 +4441,24 @@
         <f aca="false">IF(L14&gt;6,"TEA",IF(L14&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
+      <c r="N14" s="1" t="str">
+        <f aca="false">IF(L14&gt;6,"TEA",IF(L14&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
+      <c r="O14" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="P14" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q14" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(L14,P14),0)</f>
+        <v>10</v>
+      </c>
+      <c r="R14" s="5" t="str">
+        <f aca="false">IF(Q14&gt;6,"TEA",IF(Q14&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
     </row>
     <row r="15" s="1" customFormat="true" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="n">
@@ -3768,7 +4467,7 @@
       <c r="B15" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C15" s="5" t="n">
+      <c r="C15" s="1" t="n">
         <v>10</v>
       </c>
       <c r="E15" s="1" t="n">
@@ -3791,15 +4490,33 @@
         <f aca="false">IF(L15&gt;6,"TEA",IF(L15&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
+      <c r="N15" s="1" t="str">
+        <f aca="false">IF(L15&gt;6,"TEA",IF(L15&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
+      <c r="O15" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="P15" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q15" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(L15,P15),0)</f>
+        <v>10</v>
+      </c>
+      <c r="R15" s="5" t="str">
+        <f aca="false">IF(Q15&gt;6,"TEA",IF(Q15&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
     </row>
     <row r="16" s="1" customFormat="true" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="n">
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="C16" s="5" t="n">
+        <v>115</v>
+      </c>
+      <c r="C16" s="1" t="n">
         <v>8</v>
       </c>
       <c r="D16" s="3" t="n">
@@ -3834,6 +4551,24 @@
         <f aca="false">IF(L16&gt;6,"TEA",IF(L16&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
+      <c r="N16" s="1" t="str">
+        <f aca="false">IF(L16&gt;6,"TEA",IF(L16&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
+      <c r="O16" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="P16" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q16" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(L16,P16),0)</f>
+        <v>9</v>
+      </c>
+      <c r="R16" s="5" t="str">
+        <f aca="false">IF(Q16&gt;6,"TEA",IF(Q16&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
     </row>
     <row r="17" s="1" customFormat="true" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="n">
@@ -3842,14 +4577,17 @@
       <c r="B17" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C17" s="5" t="n">
+      <c r="C17" s="1" t="n">
         <v>6</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>46171</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>46171</v>
       </c>
       <c r="G17" s="1" t="n">
         <v>7</v>
@@ -3862,11 +4600,29 @@
       </c>
       <c r="L17" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(C17,E17,G17,I17,K17),0)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M17" s="1" t="str">
         <f aca="false">IF(L17&gt;6,"TEA",IF(L17&gt;3,"TEP","TED"))</f>
-        <v>TEP</v>
+        <v>TEA</v>
+      </c>
+      <c r="N17" s="1" t="str">
+        <f aca="false">IF(L17&gt;6,"TEA",IF(L17&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
+      <c r="O17" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="P17" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q17" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(L17,P17),0)</f>
+        <v>8</v>
+      </c>
+      <c r="R17" s="5" t="str">
+        <f aca="false">IF(Q17&gt;6,"TEA",IF(Q17&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="true" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3876,7 +4632,7 @@
       <c r="B18" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="C18" s="5" t="n">
+      <c r="C18" s="1" t="n">
         <v>8</v>
       </c>
       <c r="E18" s="1" t="n">
@@ -3899,6 +4655,24 @@
         <f aca="false">IF(L18&gt;6,"TEA",IF(L18&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
+      <c r="N18" s="1" t="str">
+        <f aca="false">IF(L18&gt;6,"TEA",IF(L18&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
+      <c r="O18" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="P18" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q18" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(L18,P18),0)</f>
+        <v>9</v>
+      </c>
+      <c r="R18" s="5" t="str">
+        <f aca="false">IF(Q18&gt;6,"TEA",IF(Q18&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
     </row>
     <row r="19" s="1" customFormat="true" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="n">
@@ -3907,7 +4681,7 @@
       <c r="B19" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C19" s="5" t="n">
+      <c r="C19" s="1" t="n">
         <v>9</v>
       </c>
       <c r="E19" s="1" t="n">
@@ -3917,19 +4691,40 @@
         <v>1</v>
       </c>
       <c r="I19" s="1" t="n">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="J19" s="3" t="n">
+        <v>46186</v>
       </c>
       <c r="K19" s="1" t="n">
         <v>6</v>
       </c>
       <c r="L19" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(C19,E19,G19,I19,K19),0)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M19" s="1" t="str">
         <f aca="false">IF(L19&gt;6,"TEA",IF(L19&gt;3,"TEP","TED"))</f>
         <v>TEP</v>
       </c>
+      <c r="N19" s="1" t="str">
+        <f aca="false">IF(L19&gt;6,"TEA",IF(L19&gt;3,"TEP","TED"))</f>
+        <v>TEP</v>
+      </c>
+      <c r="O19" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="P19" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q19" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(L19,P19),0)</f>
+        <v>6</v>
+      </c>
+      <c r="R19" s="5" t="str">
+        <f aca="false">IF(Q19&gt;6,"TEA",IF(Q19&gt;3,"TEP","TED"))</f>
+        <v>TEP</v>
+      </c>
     </row>
     <row r="20" s="1" customFormat="true" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="n">
@@ -3938,7 +4733,7 @@
       <c r="B20" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C20" s="5" t="n">
+      <c r="C20" s="1" t="n">
         <v>8</v>
       </c>
       <c r="D20" s="3" t="n">
@@ -3954,19 +4749,40 @@
         <v>9</v>
       </c>
       <c r="I20" s="1" t="n">
-        <v>1</v>
+        <v>9</v>
+      </c>
+      <c r="J20" s="3" t="n">
+        <v>46160</v>
       </c>
       <c r="K20" s="1" t="n">
         <v>8</v>
       </c>
       <c r="L20" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(C20,E20,G20,I20,K20),0)</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M20" s="1" t="str">
         <f aca="false">IF(L20&gt;6,"TEA",IF(L20&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
+      <c r="N20" s="1" t="str">
+        <f aca="false">IF(L20&gt;6,"TEA",IF(L20&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
+      <c r="O20" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="P20" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q20" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(L20,P20),0)</f>
+        <v>10</v>
+      </c>
+      <c r="R20" s="5" t="str">
+        <f aca="false">IF(Q20&gt;6,"TEA",IF(Q20&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
     </row>
     <row r="21" s="1" customFormat="true" ht="21.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="n">
@@ -3975,7 +4791,7 @@
       <c r="B21" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C21" s="5" t="n">
+      <c r="C21" s="1" t="n">
         <v>1</v>
       </c>
       <c r="E21" s="1" t="n">
@@ -3998,6 +4814,24 @@
         <f aca="false">IF(L21&gt;6,"TEA",IF(L21&gt;3,"TEP","TED"))</f>
         <v>TED</v>
       </c>
+      <c r="N21" s="1" t="str">
+        <f aca="false">IF(L21&gt;6,"TEA",IF(L21&gt;3,"TEP","TED"))</f>
+        <v>TED</v>
+      </c>
+      <c r="O21" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="P21" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q21" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(L21,P21),0)</f>
+        <v>5</v>
+      </c>
+      <c r="R21" s="5" t="str">
+        <f aca="false">IF(Q21&gt;6,"TEA",IF(Q21&gt;3,"TEP","TED"))</f>
+        <v>TEP</v>
+      </c>
     </row>
     <row r="22" s="1" customFormat="true" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="n">
@@ -4006,7 +4840,7 @@
       <c r="B22" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C22" s="5" t="n">
+      <c r="C22" s="1" t="n">
         <v>9</v>
       </c>
       <c r="E22" s="1" t="n">
@@ -4029,6 +4863,24 @@
         <f aca="false">IF(L22&gt;6,"TEA",IF(L22&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
+      <c r="N22" s="1" t="str">
+        <f aca="false">IF(L22&gt;6,"TEA",IF(L22&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
+      <c r="O22" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="P22" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q22" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(L22,P22),0)</f>
+        <v>10</v>
+      </c>
+      <c r="R22" s="5" t="str">
+        <f aca="false">IF(Q22&gt;6,"TEA",IF(Q22&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
     </row>
     <row r="23" s="1" customFormat="true" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="n">
@@ -4037,7 +4889,7 @@
       <c r="B23" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C23" s="5" t="n">
+      <c r="C23" s="1" t="n">
         <v>9</v>
       </c>
       <c r="E23" s="1" t="n">
@@ -4060,6 +4912,24 @@
         <f aca="false">IF(L23&gt;6,"TEA",IF(L23&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
+      <c r="N23" s="1" t="str">
+        <f aca="false">IF(L23&gt;6,"TEA",IF(L23&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
+      <c r="O23" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="P23" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q23" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(L23,P23),0)</f>
+        <v>10</v>
+      </c>
+      <c r="R23" s="5" t="str">
+        <f aca="false">IF(Q23&gt;6,"TEA",IF(Q23&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
     </row>
     <row r="24" s="1" customFormat="true" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="n">
@@ -4068,7 +4938,7 @@
       <c r="B24" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="C24" s="5" t="n">
+      <c r="C24" s="1" t="n">
         <v>7</v>
       </c>
       <c r="E24" s="1" t="n">
@@ -4091,6 +4961,24 @@
         <f aca="false">IF(L24&gt;6,"TEA",IF(L24&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
+      <c r="N24" s="1" t="str">
+        <f aca="false">IF(L24&gt;6,"TEA",IF(L24&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
+      <c r="O24" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="P24" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q24" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(L24,P24),0)</f>
+        <v>10</v>
+      </c>
+      <c r="R24" s="5" t="str">
+        <f aca="false">IF(Q24&gt;6,"TEA",IF(Q24&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
     </row>
     <row r="25" s="1" customFormat="true" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="n">
@@ -4099,7 +4987,7 @@
       <c r="B25" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C25" s="5" t="n">
+      <c r="C25" s="1" t="n">
         <v>9</v>
       </c>
       <c r="E25" s="1" t="n">
@@ -4122,6 +5010,24 @@
         <f aca="false">IF(L25&gt;6,"TEA",IF(L25&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
+      <c r="N25" s="1" t="str">
+        <f aca="false">IF(L25&gt;6,"TEA",IF(L25&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
+      <c r="O25" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="P25" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q25" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(L25,P25),0)</f>
+        <v>10</v>
+      </c>
+      <c r="R25" s="5" t="str">
+        <f aca="false">IF(Q25&gt;6,"TEA",IF(Q25&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
     </row>
     <row r="26" s="1" customFormat="true" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="n">
@@ -4130,7 +5036,7 @@
       <c r="B26" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="C26" s="5" t="n">
+      <c r="C26" s="1" t="n">
         <v>7</v>
       </c>
       <c r="E26" s="1" t="n">
@@ -4153,6 +5059,24 @@
         <f aca="false">IF(L26&gt;6,"TEA",IF(L26&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
+      <c r="N26" s="1" t="str">
+        <f aca="false">IF(L26&gt;6,"TEA",IF(L26&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
+      <c r="O26" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="P26" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q26" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(L26,P26),0)</f>
+        <v>9</v>
+      </c>
+      <c r="R26" s="5" t="str">
+        <f aca="false">IF(Q26&gt;6,"TEA",IF(Q26&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
     </row>
     <row r="27" s="1" customFormat="true" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="n">
@@ -4161,7 +5085,7 @@
       <c r="B27" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="C27" s="5" t="n">
+      <c r="C27" s="1" t="n">
         <v>7</v>
       </c>
       <c r="E27" s="1" t="n">
@@ -4182,6 +5106,24 @@
       </c>
       <c r="M27" s="1" t="str">
         <f aca="false">IF(L27&gt;6,"TEA",IF(L27&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
+      <c r="N27" s="1" t="str">
+        <f aca="false">IF(L27&gt;6,"TEA",IF(L27&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
+      <c r="O27" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="P27" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q27" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(L27,P27),0)</f>
+        <v>7</v>
+      </c>
+      <c r="R27" s="5" t="str">
+        <f aca="false">IF(Q27&gt;6,"TEA",IF(Q27&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
     </row>
@@ -4194,60 +5136,24 @@
     <row r="34" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="35" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <conditionalFormatting sqref="C2:C27">
-    <cfRule type="cellIs" priority="2" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+  <conditionalFormatting sqref="Q2:R27">
+    <cfRule type="cellIs" priority="2" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
       <formula>6</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="between" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+    <cfRule type="cellIs" priority="3" operator="between" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
       <formula>4</formula>
       <formula>6</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="4" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+    <cfRule type="cellIs" priority="4" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
       <formula>4</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E27">
-    <cfRule type="cellIs" priority="5" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>5</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="6" operator="between" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
-      <formula>4</formula>
-      <formula>6</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="7" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
-      <formula>4</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G2:H27">
-    <cfRule type="cellIs" priority="8" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>6</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="9" operator="between" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
-      <formula>4</formula>
-      <formula>6</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="10" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
-      <formula>4</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I2:M27">
-    <cfRule type="cellIs" priority="11" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>6</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="12" operator="between" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
-      <formula>4</formula>
-      <formula>6</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="13" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
-      <formula>4</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="14" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+    <cfRule type="cellIs" priority="5" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
       <formula>"TEA"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="15" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+    <cfRule type="cellIs" priority="6" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
       <formula>"TEP"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="16" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+    <cfRule type="cellIs" priority="7" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
       <formula>"TED"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4284,16 +5190,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4335,7 +5241,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>22</v>
@@ -4959,16 +5865,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5010,7 +5916,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>22</v>
@@ -5243,7 +6149,7 @@
         <v>15</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="D19" s="1" t="n">
         <v>1</v>
@@ -5592,7 +6498,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F47" s="1" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="G47" s="1" t="n">
         <f aca="false">COUNTIF(G2:G46,"&gt;0")</f>
@@ -5633,16 +6539,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5684,7 +6590,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>22</v>
@@ -6578,16 +7484,16 @@
         <v>2</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/inasistencias-7A-CompAero/Alumnos-⁄A-CompAero.xlsx
+++ b/inasistencias-7A-CompAero/Alumnos-⁄A-CompAero.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="919" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="945" uniqueCount="121">
   <si>
     <t xml:space="preserve">nRO</t>
   </si>
@@ -802,7 +802,8 @@
     <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="14" min="6" style="1" width="8.87"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="15" min="15" style="1" width="12.55"/>
     <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="31" min="16" style="1" width="8.87"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16333" min="16332" style="0" width="10.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16332" min="16331" style="1" width="10.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16333" min="16333" style="0" width="10.58"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16334" style="1" width="10.58"/>
   </cols>
   <sheetData>
@@ -922,65 +923,63 @@
         <v>46241</v>
       </c>
       <c r="AL2" s="3" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="AM2" s="3" t="n">
-        <v>46255</v>
+        <v>46262</v>
       </c>
       <c r="AN2" s="3" t="n">
-        <v>46262</v>
+        <v>46269</v>
       </c>
       <c r="AO2" s="3" t="n">
-        <v>46269</v>
+        <v>46276</v>
       </c>
       <c r="AP2" s="3" t="n">
-        <v>46276</v>
+        <v>46283</v>
       </c>
       <c r="AQ2" s="3" t="n">
-        <v>46283</v>
+        <v>46290</v>
       </c>
       <c r="AR2" s="3" t="n">
-        <v>46290</v>
+        <v>46297</v>
       </c>
       <c r="AS2" s="3" t="n">
-        <v>46297</v>
+        <v>46304</v>
       </c>
       <c r="AT2" s="3" t="n">
-        <v>46304</v>
+        <v>46311</v>
       </c>
       <c r="AU2" s="3" t="n">
-        <v>46311</v>
+        <v>46318</v>
       </c>
       <c r="AV2" s="3" t="n">
-        <v>46318</v>
+        <v>46325</v>
       </c>
       <c r="AW2" s="3" t="n">
-        <v>46325</v>
+        <v>46332</v>
       </c>
       <c r="AX2" s="3" t="n">
-        <v>46332</v>
+        <v>46339</v>
       </c>
       <c r="AY2" s="3" t="n">
-        <v>46339</v>
+        <v>46346</v>
       </c>
       <c r="AZ2" s="3" t="n">
-        <v>46346</v>
+        <v>46353</v>
       </c>
       <c r="BA2" s="3" t="n">
-        <v>46353</v>
+        <v>46360</v>
       </c>
       <c r="BB2" s="3" t="n">
-        <v>46360</v>
+        <v>46367</v>
       </c>
       <c r="BC2" s="3" t="n">
-        <v>46367</v>
+        <v>46374</v>
       </c>
       <c r="BD2" s="3" t="n">
-        <v>46374</v>
-      </c>
-      <c r="BE2" s="3" t="n">
         <v>46381</v>
       </c>
+      <c r="BE2" s="3"/>
       <c r="BF2" s="3"/>
       <c r="BG2" s="3"/>
       <c r="BH2" s="3"/>
@@ -990,7 +989,6 @@
       <c r="BL2" s="3"/>
       <c r="BM2" s="3"/>
       <c r="BN2" s="3"/>
-      <c r="BO2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
@@ -1095,7 +1093,10 @@
       <c r="AJ3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="AK3" s="6" t="s">
+      <c r="AK3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AL3" s="6" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1184,7 +1185,10 @@
       <c r="AJ4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="AK4" s="6" t="s">
+      <c r="AK4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AL4" s="6" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1285,7 +1289,10 @@
       <c r="AJ5" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="AK5" s="6" t="s">
+      <c r="AK5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AL5" s="6" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1386,7 +1393,10 @@
       <c r="AJ6" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="AK6" s="6" t="s">
+      <c r="AK6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AL6" s="6" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1484,7 +1494,10 @@
       <c r="AJ7" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AK7" s="6" t="s">
+      <c r="AK7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AL7" s="6" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1576,7 +1589,10 @@
       <c r="AJ8" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="AK8" s="6" t="s">
+      <c r="AK8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AL8" s="6" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1668,7 +1684,10 @@
       <c r="AJ9" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="AK9" s="6" t="s">
+      <c r="AK9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AL9" s="6" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1763,7 +1782,10 @@
       <c r="AJ10" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="AK10" s="6" t="s">
+      <c r="AK10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AL10" s="6" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1852,7 +1874,10 @@
       <c r="AJ11" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AK11" s="6" t="s">
+      <c r="AK11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AL11" s="6" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1947,8 +1972,11 @@
       <c r="AJ12" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="AK12" s="6" t="s">
-        <v>15</v>
+      <c r="AK12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AL12" s="6" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2036,7 +2064,10 @@
       <c r="AJ13" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="AK13" s="6" t="s">
+      <c r="AK13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AL13" s="6" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2134,8 +2165,11 @@
       <c r="AJ14" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="AK14" s="6" t="s">
-        <v>17</v>
+      <c r="AK14" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AL14" s="6" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2223,7 +2257,10 @@
       <c r="AJ15" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AK15" s="6" t="s">
+      <c r="AK15" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AL15" s="6" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2312,8 +2349,11 @@
       <c r="AJ16" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="AK16" s="6" t="s">
-        <v>15</v>
+      <c r="AK16" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AL16" s="6" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2404,7 +2444,10 @@
       <c r="AJ17" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="AK17" s="6" t="s">
+      <c r="AK17" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AL17" s="6" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2502,7 +2545,10 @@
       <c r="AJ18" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="AK18" s="6" t="s">
+      <c r="AK18" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AL18" s="6" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2594,8 +2640,11 @@
       <c r="AJ19" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AK19" s="6" t="s">
-        <v>15</v>
+      <c r="AK19" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AL19" s="6" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2689,7 +2738,10 @@
       <c r="AJ20" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="AK20" s="6" t="s">
+      <c r="AK20" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AL20" s="6" t="s">
         <v>17</v>
       </c>
     </row>
@@ -2781,7 +2833,9 @@
       <c r="AK21" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="XDD21" s="0"/>
+      <c r="AL21" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="XDE21" s="0"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2875,7 +2929,10 @@
       <c r="AJ22" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="AK22" s="6" t="s">
+      <c r="AK22" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AL22" s="6" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2967,7 +3024,10 @@
       <c r="AJ23" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="AK23" s="6" t="s">
+      <c r="AK23" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AL23" s="6" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3059,7 +3119,10 @@
       <c r="AJ24" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="AK24" s="6" t="s">
+      <c r="AK24" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AL24" s="6" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3151,7 +3214,10 @@
       <c r="AJ25" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="AK25" s="6" t="s">
+      <c r="AK25" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AL25" s="6" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3240,7 +3306,10 @@
       <c r="AJ26" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AK26" s="6" t="s">
+      <c r="AK26" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AL26" s="6" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3335,8 +3404,11 @@
       <c r="AJ27" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="AK27" s="6" t="s">
-        <v>15</v>
+      <c r="AK27" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AL27" s="6" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3436,7 +3508,10 @@
       <c r="AJ28" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="AK28" s="6" t="s">
+      <c r="AK28" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AL28" s="6" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3502,10 +3577,16 @@
       </c>
       <c r="AI29" s="1"/>
       <c r="AJ29" s="1" t="n">
-        <v>11</v>
+        <f aca="false">COUNTIF(AJ3:AJ28,"p")</f>
+        <v>5</v>
       </c>
       <c r="AK29" s="1" t="n">
-        <v>11</v>
+        <f aca="false">COUNTIF(AK3:AK28,"p")</f>
+        <v>23</v>
+      </c>
+      <c r="AL29" s="1" t="n">
+        <f aca="false">COUNTIF(AL3:AL28,"p")</f>
+        <v>21</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3570,9 +3651,15 @@
       </c>
       <c r="AI30" s="1"/>
       <c r="AJ30" s="1" t="n">
+        <f aca="false">COUNTIF(AJ3:AJ28,"M")</f>
         <v>0</v>
       </c>
       <c r="AK30" s="1" t="n">
+        <f aca="false">COUNTIF(AK3:AK28,"M")</f>
+        <v>0</v>
+      </c>
+      <c r="AL30" s="1" t="n">
+        <f aca="false">COUNTIF(AL3:AL28,"M")</f>
         <v>0</v>
       </c>
     </row>
@@ -3638,9 +3725,15 @@
       </c>
       <c r="AI31" s="1"/>
       <c r="AJ31" s="1" t="n">
+        <f aca="false">COUNTIF(AJ3:AJ28,"T")</f>
         <v>0</v>
       </c>
       <c r="AK31" s="1" t="n">
+        <f aca="false">COUNTIF(AK3:AK28,"T")</f>
+        <v>0</v>
+      </c>
+      <c r="AL31" s="1" t="n">
+        <f aca="false">COUNTIF(AL3:AL28,"T")</f>
         <v>0</v>
       </c>
     </row>
@@ -3706,10 +3799,16 @@
       </c>
       <c r="AI32" s="1"/>
       <c r="AJ32" s="1" t="n">
-        <v>11</v>
+        <f aca="false">SUM(AJ29:AJ31)</f>
+        <v>5</v>
       </c>
       <c r="AK32" s="1" t="n">
-        <v>11</v>
+        <f aca="false">SUM(AK29:AK31)</f>
+        <v>23</v>
+      </c>
+      <c r="AL32" s="1" t="n">
+        <f aca="false">SUM(AL29:AL31)</f>
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/inasistencias-7A-CompAero/Alumnos-⁄A-CompAero.xlsx
+++ b/inasistencias-7A-CompAero/Alumnos-⁄A-CompAero.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="945" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1050" uniqueCount="121">
   <si>
     <t xml:space="preserve">nRO</t>
   </si>
@@ -504,11 +504,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -791,7 +791,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:XDE32"/>
+  <dimension ref="A1:BN32"/>
   <sheetFormatPr defaultColWidth="8.87109375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4.87"/>
@@ -802,9 +802,7 @@
     <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="14" min="6" style="1" width="8.87"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="15" min="15" style="1" width="12.55"/>
     <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="31" min="16" style="1" width="8.87"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16332" min="16331" style="1" width="10.58"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16333" min="16333" style="0" width="10.58"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16334" style="1" width="10.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16331" style="1" width="10.58"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -932,13 +930,13 @@
         <v>46269</v>
       </c>
       <c r="AO2" s="3" t="n">
-        <v>46276</v>
+        <v>46283</v>
       </c>
       <c r="AP2" s="3" t="n">
-        <v>46283</v>
-      </c>
-      <c r="AQ2" s="3" t="n">
         <v>46290</v>
+      </c>
+      <c r="AQ2" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AR2" s="3" t="n">
         <v>46297</v>
@@ -1096,9 +1094,22 @@
       <c r="AK3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AL3" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="AL3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AM3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AN3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AO3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AP3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AQ3" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="n">
@@ -1107,7 +1118,7 @@
       <c r="B4" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="6" t="s">
         <v>19</v>
       </c>
       <c r="D4" s="2" t="s">
@@ -1188,9 +1199,22 @@
       <c r="AK4" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AL4" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="AL4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AM4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AN4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AO4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AP4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AQ4" s="2"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="n">
@@ -1292,9 +1316,22 @@
       <c r="AK5" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AL5" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="AL5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AM5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AN5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AO5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AP5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AQ5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="n">
@@ -1396,9 +1433,22 @@
       <c r="AK6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AL6" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="AL6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AM6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AN6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AO6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AP6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AQ6" s="2"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="n">
@@ -1497,9 +1547,22 @@
       <c r="AK7" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AL7" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="AL7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AM7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AN7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AO7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AP7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AQ7" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="n">
@@ -1592,8 +1655,23 @@
       <c r="AK8" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AL8" s="6" t="s">
-        <v>15</v>
+      <c r="AL8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AM8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AN8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AO8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AP8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AQ8" s="7" t="n">
+        <v>0.666666666666667</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1687,9 +1765,22 @@
       <c r="AK9" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AL9" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="AL9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AM9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AN9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AO9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AP9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AQ9" s="2"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="n">
@@ -1785,9 +1876,22 @@
       <c r="AK10" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AL10" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="AL10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AM10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AN10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AO10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AP10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AQ10" s="2"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="n">
@@ -1877,9 +1981,22 @@
       <c r="AK11" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AL11" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="AL11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AM11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AN11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AO11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AP11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AQ11" s="2"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="n">
@@ -1975,9 +2092,22 @@
       <c r="AK12" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AL12" s="6" t="s">
-        <v>17</v>
-      </c>
+      <c r="AL12" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AM12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AN12" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AO12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AP12" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AQ12" s="2"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="n">
@@ -2067,9 +2197,22 @@
       <c r="AK13" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AL13" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="AL13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AM13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AN13" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AO13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AP13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AQ13" s="2"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="n">
@@ -2168,9 +2311,22 @@
       <c r="AK14" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="AL14" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="AL14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AM14" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AN14" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AO14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AP14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AQ14" s="2"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="n">
@@ -2260,9 +2416,22 @@
       <c r="AK15" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AL15" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="AL15" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AM15" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AN15" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AO15" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AP15" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AQ15" s="2"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="n">
@@ -2352,9 +2521,22 @@
       <c r="AK16" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AL16" s="6" t="s">
-        <v>17</v>
-      </c>
+      <c r="AL16" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AM16" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AN16" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AO16" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AP16" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AQ16" s="2"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="n">
@@ -2447,9 +2629,22 @@
       <c r="AK17" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AL17" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="AL17" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AM17" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AN17" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AO17" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AP17" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AQ17" s="2"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="n">
@@ -2548,9 +2743,22 @@
       <c r="AK18" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AL18" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="AL18" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AM18" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AN18" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AO18" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AP18" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AQ18" s="2"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="n">
@@ -2643,9 +2851,22 @@
       <c r="AK19" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AL19" s="6" t="s">
-        <v>17</v>
-      </c>
+      <c r="AL19" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AM19" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AN19" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AO19" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AP19" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AQ19" s="2"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="n">
@@ -2741,8 +2962,23 @@
       <c r="AK20" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="AL20" s="6" t="s">
-        <v>17</v>
+      <c r="AL20" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AM20" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AN20" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AO20" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AP20" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AQ20" s="7" t="n">
+        <v>0.666666666666667</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2836,7 +3072,18 @@
       <c r="AL21" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="XDE21" s="0"/>
+      <c r="AM21" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AN21" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AO21" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AP21" s="1" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="n">
@@ -2932,9 +3179,22 @@
       <c r="AK22" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AL22" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="AL22" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AM22" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AN22" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AO22" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AP22" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AQ22" s="2"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="n">
@@ -3027,9 +3287,22 @@
       <c r="AK23" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AL23" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="AL23" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AM23" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AN23" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AO23" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AP23" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AQ23" s="2"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="n">
@@ -3122,9 +3395,22 @@
       <c r="AK24" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AL24" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="AL24" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AM24" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AN24" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AO24" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AP24" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AQ24" s="2"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="n">
@@ -3217,9 +3503,22 @@
       <c r="AK25" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AL25" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="AL25" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AM25" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AN25" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AO25" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AP25" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AQ25" s="2"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="n">
@@ -3309,9 +3608,22 @@
       <c r="AK26" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AL26" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="AL26" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AM26" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AN26" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AO26" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AP26" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AQ26" s="2"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="n">
@@ -3407,9 +3719,22 @@
       <c r="AK27" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AL27" s="6" t="s">
-        <v>17</v>
-      </c>
+      <c r="AL27" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AM27" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AN27" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AO27" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AP27" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AQ27" s="2"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="n">
@@ -3511,9 +3836,22 @@
       <c r="AK28" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AL28" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="AL28" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AM28" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AN28" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AO28" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AP28" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AQ28" s="2"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C29" s="1" t="s">
@@ -3588,6 +3926,23 @@
         <f aca="false">COUNTIF(AL3:AL28,"p")</f>
         <v>21</v>
       </c>
+      <c r="AM29" s="1" t="n">
+        <f aca="false">COUNTIF(AM3:AM28,"p")</f>
+        <v>18</v>
+      </c>
+      <c r="AN29" s="1" t="n">
+        <f aca="false">COUNTIF(AN3:AN28,"p")</f>
+        <v>15</v>
+      </c>
+      <c r="AO29" s="1" t="n">
+        <f aca="false">COUNTIF(AO3:AO28,"p")</f>
+        <v>21</v>
+      </c>
+      <c r="AP29" s="1" t="n">
+        <f aca="false">COUNTIF(AP3:AP28,"p")</f>
+        <v>16</v>
+      </c>
+      <c r="AQ29" s="1"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C30" s="1" t="s">
@@ -3662,6 +4017,23 @@
         <f aca="false">COUNTIF(AL3:AL28,"M")</f>
         <v>0</v>
       </c>
+      <c r="AM30" s="1" t="n">
+        <f aca="false">COUNTIF(AM3:AM28,"M")</f>
+        <v>0</v>
+      </c>
+      <c r="AN30" s="1" t="n">
+        <f aca="false">COUNTIF(AN3:AN28,"M")</f>
+        <v>0</v>
+      </c>
+      <c r="AO30" s="1" t="n">
+        <f aca="false">COUNTIF(AO3:AO28,"M")</f>
+        <v>0</v>
+      </c>
+      <c r="AP30" s="1" t="n">
+        <f aca="false">COUNTIF(AP3:AP28,"M")</f>
+        <v>0</v>
+      </c>
+      <c r="AQ30" s="1"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C31" s="1" t="s">
@@ -3736,6 +4108,23 @@
         <f aca="false">COUNTIF(AL3:AL28,"T")</f>
         <v>0</v>
       </c>
+      <c r="AM31" s="1" t="n">
+        <f aca="false">COUNTIF(AM3:AM28,"T")</f>
+        <v>0</v>
+      </c>
+      <c r="AN31" s="1" t="n">
+        <f aca="false">COUNTIF(AN3:AN28,"T")</f>
+        <v>0</v>
+      </c>
+      <c r="AO31" s="1" t="n">
+        <f aca="false">COUNTIF(AO3:AO28,"T")</f>
+        <v>0</v>
+      </c>
+      <c r="AP31" s="1" t="n">
+        <f aca="false">COUNTIF(AP3:AP28,"T")</f>
+        <v>2</v>
+      </c>
+      <c r="AQ31" s="1"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C32" s="1" t="s">
@@ -3810,6 +4199,23 @@
         <f aca="false">SUM(AL29:AL31)</f>
         <v>21</v>
       </c>
+      <c r="AM32" s="1" t="n">
+        <f aca="false">SUM(AM29:AM31)</f>
+        <v>18</v>
+      </c>
+      <c r="AN32" s="1" t="n">
+        <f aca="false">SUM(AN29:AN31)</f>
+        <v>15</v>
+      </c>
+      <c r="AO32" s="1" t="n">
+        <f aca="false">SUM(AO29:AO31)</f>
+        <v>21</v>
+      </c>
+      <c r="AP32" s="1" t="n">
+        <f aca="false">SUM(AP29:AP31)</f>
+        <v>18</v>
+      </c>
+      <c r="AQ32" s="1"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="AC3:AC28">
@@ -3960,7 +4366,7 @@
       <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="6" t="s">
         <v>19</v>
       </c>
       <c r="C3" s="1" t="n">
@@ -5322,7 +5728,7 @@
       <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="6" t="s">
         <v>19</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -5997,7 +6403,7 @@
       <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="6" t="s">
         <v>19</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -6671,7 +7077,7 @@
       <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="6" t="s">
         <v>19</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -7616,7 +8022,7 @@
       <c r="A6" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="6" t="s">
         <v>19</v>
       </c>
       <c r="C6" s="1" t="s">
